--- a/artfynd/A 45023-2023 artfynd.xlsx
+++ b/artfynd/A 45023-2023 artfynd.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rode Nordin, Eva Norén</t>
+          <t>Rode Nordin, Eva Norén, Peter Berglund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 45023-2023 artfynd.xlsx
+++ b/artfynd/A 45023-2023 artfynd.xlsx
@@ -723,7 +723,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Västra Kolgården, Högsjömon, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">

--- a/artfynd/A 45023-2023 artfynd.xlsx
+++ b/artfynd/A 45023-2023 artfynd.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rode Nordin, Eva Norén, Peter Berglund</t>
+          <t>Eva Norén, Rode Nordin, Peter Berglund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 45023-2023 artfynd.xlsx
+++ b/artfynd/A 45023-2023 artfynd.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Norén, Rode Nordin, Peter Berglund</t>
+          <t>Rode Nordin, Eva Norén, Peter Berglund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
